--- a/nr-prepare-release/ig/StructureDefinition-nde-subscription.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-nde-subscription.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:04:13+00:00</t>
+    <t>2026-03-13T15:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release/ig/StructureDefinition-nde-subscription.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-nde-subscription.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:06:50+00:00</t>
+    <t>2026-03-13T15:11:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release/ig/StructureDefinition-nde-subscription.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-nde-subscription.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:11:04+00:00</t>
+    <t>2026-03-13T15:32:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release/ig/StructureDefinition-nde-subscription.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-nde-subscription.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:32:58+00:00</t>
+    <t>2026-03-13T16:09:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
